--- a/artfynd/A 24233-2026 artfynd.xlsx
+++ b/artfynd/A 24233-2026 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>114045486</v>
       </c>
       <c r="B2" t="n">
-        <v>79464</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,12 +775,7 @@
         <v>114045487</v>
       </c>
       <c r="B3" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24233-2026 artfynd.xlsx
+++ b/artfynd/A 24233-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114045486</v>
+        <v>135212939</v>
       </c>
       <c r="B2" t="n">
-        <v>80336</v>
+        <v>79373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hällstensberget, Nb</t>
+          <t>Skogbergmyran, Skogbergmyran, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>799398</v>
+        <v>799400</v>
       </c>
       <c r="R2" t="n">
-        <v>7324729</v>
+        <v>7324705</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,57 +760,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Frédéric Forsmark</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114045487</v>
+        <v>135213101</v>
       </c>
       <c r="B3" t="n">
-        <v>57953</v>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hällstensberget, Nb</t>
+          <t>Skogbergmyran, Skogbergmyran, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>799460</v>
+        <v>799389</v>
       </c>
       <c r="R3" t="n">
-        <v>7324805</v>
+        <v>7324726</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -837,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -857,15 +857,1586 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135214312</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Skogbergmyran, Skogbergmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>799526</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7324652</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135214429</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skogbergmyran, Skogbergmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>799523</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7324639</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>114045486</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hällstensberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>799398</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7324729</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Robert Sandberg</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Frédéric Forsmark</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>114045487</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hällstensberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>799460</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7324805</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Frédéric Forsmark</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135214236</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skogbergmyran, Skogbergmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>799497</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7324707</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135214485</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Skogbergmyran, Skogbergmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>799526</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7324625</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135213475</v>
+      </c>
+      <c r="B10" t="n">
+        <v>8449</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Skogbergmyran, Skogbergmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>799442</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7324807</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135212137</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Skogbergmyran, Skogbergmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>799477</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7324677</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135212467</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Skogbergmyran, Skogbergmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>799430</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7324727</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135213074</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Skogbergmyran, Skogbergmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>799384</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7324720</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135212269</v>
+      </c>
+      <c r="B14" t="n">
+        <v>108205</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Skogbergmyran, Skogbergmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>799440</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7324702</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135213134</v>
+      </c>
+      <c r="B15" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Skogbergmyran, Skogbergmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>799391</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7324735</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135212724</v>
+      </c>
+      <c r="B16" t="n">
+        <v>109924</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221184</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Torta</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lactuca alpina</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Skogbergmyran, Skogbergmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>799406</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7324705</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135213013</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99472</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Skogbergmyran, Skogbergmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>799394</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7324718</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135213046</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Skogbergmyran, Skogbergmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>799390</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7324712</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135213029</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98249</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Skogbergmyran, Skogbergmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>799401</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7324716</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24233-2026 artfynd.xlsx
+++ b/artfynd/A 24233-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135212939</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135213101</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135214312</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135214429</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045486</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045487</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1360,6 +1395,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135214236</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1462,6 +1502,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135214485</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1564,6 +1609,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135213475</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1661,6 +1711,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135212137</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1758,6 +1813,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135212467</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1855,6 +1915,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135213074</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1952,6 +2017,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135212269</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2049,6 +2119,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135213134</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2146,6 +2221,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135212724</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2243,6 +2323,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135213013</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2340,6 +2425,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135213046</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2437,8 +2527,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135213029</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 24233-2026 artfynd.xlsx
+++ b/artfynd/A 24233-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135212939</v>
       </c>
       <c r="B2" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135213101</v>
       </c>
       <c r="B3" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135214312</v>
       </c>
       <c r="B4" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135214429</v>
       </c>
       <c r="B5" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135214236</v>
       </c>
       <c r="B8" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>135214485</v>
       </c>
       <c r="B9" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>135213475</v>
       </c>
       <c r="B10" t="n">
-        <v>8449</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>135212137</v>
       </c>
       <c r="B11" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>135212467</v>
       </c>
       <c r="B12" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>135213074</v>
       </c>
       <c r="B13" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>135212269</v>
       </c>
       <c r="B14" t="n">
-        <v>108205</v>
+        <v>108260</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>135213134</v>
       </c>
       <c r="B15" t="n">
-        <v>111153</v>
+        <v>111210</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>135212724</v>
       </c>
       <c r="B16" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>135213013</v>
       </c>
       <c r="B17" t="n">
-        <v>99472</v>
+        <v>99519</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>135213046</v>
       </c>
       <c r="B18" t="n">
-        <v>99001</v>
+        <v>99048</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>135213029</v>
       </c>
       <c r="B19" t="n">
-        <v>98249</v>
+        <v>98293</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 24233-2026 artfynd.xlsx
+++ b/artfynd/A 24233-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135212939</v>
       </c>
       <c r="B2" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135213101</v>
       </c>
       <c r="B3" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135214312</v>
       </c>
       <c r="B4" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135214429</v>
       </c>
       <c r="B5" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>135212137</v>
       </c>
       <c r="B11" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>135212467</v>
       </c>
       <c r="B12" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>135213074</v>
       </c>
       <c r="B13" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>135212269</v>
       </c>
       <c r="B14" t="n">
-        <v>108260</v>
+        <v>108287</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>135213134</v>
       </c>
       <c r="B15" t="n">
-        <v>111210</v>
+        <v>111237</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>135212724</v>
       </c>
       <c r="B16" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>135213013</v>
       </c>
       <c r="B17" t="n">
-        <v>99519</v>
+        <v>99546</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>135213046</v>
       </c>
       <c r="B18" t="n">
-        <v>99048</v>
+        <v>99075</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>135213029</v>
       </c>
       <c r="B19" t="n">
-        <v>98293</v>
+        <v>98320</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 24233-2026 artfynd.xlsx
+++ b/artfynd/A 24233-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,45 +680,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114045486</v>
+        <v>135212939</v>
       </c>
       <c r="B2" t="n">
-        <v>80336</v>
+        <v>79441</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hällstensberget, Nb</t>
+          <t>Skogbergmyran, Skogbergmyran, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>799398</v>
+        <v>799400</v>
       </c>
       <c r="R2" t="n">
-        <v>7324729</v>
+        <v>7324705</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,62 +765,62 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Frédéric Forsmark</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114045486</t>
+          <t>https://artportalen.se/Sighting/135212939</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114045487</v>
+        <v>135213101</v>
       </c>
       <c r="B3" t="n">
-        <v>57953</v>
+        <v>79441</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hällstensberget, Nb</t>
+          <t>Skogbergmyran, Skogbergmyran, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>799460</v>
+        <v>799389</v>
       </c>
       <c r="R3" t="n">
-        <v>7324805</v>
+        <v>7324726</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,18 +867,1669 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Frédéric Forsmark</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135213101</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135214312</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Skogbergmyran, Skogbergmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>799526</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7324652</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135214312</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135214429</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skogbergmyran, Skogbergmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>799523</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7324639</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135214429</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>114045486</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hällstensberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>799398</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7324729</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Frédéric Forsmark</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045486</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>114045487</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hällstensberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>799460</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7324805</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Frédéric Forsmark</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/114045487</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135214236</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skogbergmyran, Skogbergmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>799497</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7324707</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135214236</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135214485</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Skogbergmyran, Skogbergmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>799526</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7324625</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135214485</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135213475</v>
+      </c>
+      <c r="B10" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Skogbergmyran, Skogbergmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>799442</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7324807</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135213475</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135212137</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99191</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Skogbergmyran, Skogbergmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>799477</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7324677</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135212137</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135212467</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99191</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Skogbergmyran, Skogbergmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>799430</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7324727</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135212467</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135213074</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99191</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Skogbergmyran, Skogbergmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>799384</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7324720</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135213074</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135212269</v>
+      </c>
+      <c r="B14" t="n">
+        <v>108292</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Skogbergmyran, Skogbergmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>799440</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7324702</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135212269</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135213134</v>
+      </c>
+      <c r="B15" t="n">
+        <v>111242</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Skogbergmyran, Skogbergmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>799391</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7324735</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135213134</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135212724</v>
+      </c>
+      <c r="B16" t="n">
+        <v>110012</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221184</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Torta</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lactuca alpina</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Skogbergmyran, Skogbergmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>799406</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7324705</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135212724</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135213013</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99551</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Skogbergmyran, Skogbergmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>799394</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7324718</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135213013</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135213046</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99080</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Skogbergmyran, Skogbergmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>799390</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7324712</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135213046</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135213029</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98325</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Skogbergmyran, Skogbergmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>799401</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7324716</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135213029</t>
         </is>
       </c>
     </row>
@@ -886,6 +2537,22 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24233-2026 artfynd.xlsx
+++ b/artfynd/A 24233-2026 artfynd.xlsx
@@ -1620,7 +1620,7 @@
         <v>135212137</v>
       </c>
       <c r="B11" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>135212467</v>
       </c>
       <c r="B12" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>135213074</v>
       </c>
       <c r="B13" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>135212269</v>
       </c>
       <c r="B14" t="n">
-        <v>108292</v>
+        <v>108294</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>135213134</v>
       </c>
       <c r="B15" t="n">
-        <v>111242</v>
+        <v>111244</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>135212724</v>
       </c>
       <c r="B16" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>135213013</v>
       </c>
       <c r="B17" t="n">
-        <v>99551</v>
+        <v>99553</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>135213046</v>
       </c>
       <c r="B18" t="n">
-        <v>99080</v>
+        <v>99082</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>135213029</v>
       </c>
       <c r="B19" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
